--- a/Lesson_development/input_data/wur_missing_in_pure_input_dataset.xlsx
+++ b/Lesson_development/input_data/wur_missing_in_pure_input_dataset.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/linigodelacruz_tudelft_nl/Documents/Documents/4TU.ResearchData/Projects/TRAINING/WebAPI_with_uses_cases/USES-CASES/Sync_Pure_4TU_WUR/Lesson_development/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/linigodelacruz_tudelft_nl/Documents/Documents/4TU.ResearchData/Projects/TRAINING/WebAPI_with_uses_cases/USES-CASES/Sync_Pure_4TU_WUR/Lesson_development/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7DBC8FC-C3C3-4EA4-8677-AB71D66D5403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{B7DBC8FC-C3C3-4EA4-8677-AB71D66D5403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDA706A8-63FC-4A63-8DEB-0844218A2FD2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BCDA7FC-73B3-413F-9949-58264D9F73C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$35</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -851,10 +854,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7471BAA6-727F-4EB7-9B15-10E3C2E4F339}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="73.42578125" customWidth="1"/>
+    <col min="1" max="1" width="94.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="8" max="8" width="36.28515625" customWidth="1"/>
+    <col min="9" max="9" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -886,7 +898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -915,7 +927,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -944,7 +956,7 @@
         <v>45197</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1489,6 +1501,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="D1:D35" xr:uid="{7471BAA6-727F-4EB7-9B15-10E3C2E4F339}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>